--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="477">
   <si>
     <t>Filename</t>
   </si>
@@ -808,634 +808,643 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9858,0.0017,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.7687,0.0006,0.0629,0.0541</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.1448,0.0028,0.3695,0.3935</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9755,0.0022,0.0114,0.0003</t>
+  </si>
+  <si>
+    <t>0.7347,0.0006,0.1470,0.0258</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4456,0.0030,0.1997,0.1779</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9815,0.0005,0.0116,0.0000</t>
+  </si>
+  <si>
+    <t>0.9387,0.0016,0.0515,0.0000</t>
+  </si>
+  <si>
+    <t>0.7663,0.0017,0.2716,0.0000</t>
+  </si>
+  <si>
+    <t>0.3696,0.0016,0.7482,0.0000</t>
+  </si>
+  <si>
+    <t>0.9234,0.0010,0.1022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0073,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9942,0.0171,0.0000</t>
+  </si>
+  <si>
+    <t>0.3228,0.5772,0.0227,0.0001</t>
+  </si>
+  <si>
+    <t>0.0051,0.9904,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9983,0.0045,0.0000</t>
+  </si>
+  <si>
+    <t>0.4247,0.0007,0.7069,0.0000</t>
+  </si>
+  <si>
+    <t>0.9653,0.0002,0.0382,0.0000</t>
+  </si>
+  <si>
+    <t>0.3300,0.0005,0.7879,0.0001</t>
+  </si>
+  <si>
+    <t>0.3561,0.0010,0.7545,0.0001</t>
+  </si>
+  <si>
+    <t>0.5744,0.0003,0.6252,0.0000</t>
+  </si>
+  <si>
+    <t>0.7913,0.0002,0.3773,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.8955,0.0838,0.0045,0.0000</t>
+  </si>
+  <si>
+    <t>0.9824,0.0025,0.0061,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0133,0.8100,0.1659,0.0000</t>
+  </si>
+  <si>
+    <t>0.9887,0.0039,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.4384,0.0043,0.5794,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0070,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0762,0.4372,0.3531,0.0001</t>
+  </si>
+  <si>
+    <t>0.0349,0.0673,0.8367,0.0002</t>
+  </si>
+  <si>
+    <t>0.0207,0.8297,0.1273,0.0009</t>
+  </si>
+  <si>
+    <t>0.0642,0.0010,0.9505,0.0001</t>
+  </si>
+  <si>
+    <t>0.4021,0.0002,0.7614,0.0000</t>
+  </si>
+  <si>
+    <t>0.0436,0.0242,0.8953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9984,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0101,0.0005,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.1245,0.5180,0.1873,0.0062</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9956,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.0023,0.9917,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0157,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.3673,0.0006,0.7717,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0001,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0280,0.0005,0.9826,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0017,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.0004,0.9806,0.0012</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9738,0.0012,0.0130,0.0000</t>
-  </si>
-  <si>
-    <t>0.9739,0.0006,0.0222,0.0000</t>
-  </si>
-  <si>
-    <t>0.9270,0.0010,0.0785,0.0000</t>
-  </si>
-  <si>
-    <t>0.4464,0.0018,0.6799,0.0000</t>
-  </si>
-  <si>
-    <t>0.9663,0.0006,0.0364,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9978,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.0115,0.9732,0.0392,0.0000</t>
-  </si>
-  <si>
-    <t>0.7102,0.2715,0.0070,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.9906,0.0057,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.5383,0.0014,0.5604,0.0002</t>
-  </si>
-  <si>
-    <t>0.9106,0.0011,0.0981,0.0001</t>
-  </si>
-  <si>
-    <t>0.1246,0.0016,0.9113,0.0001</t>
-  </si>
-  <si>
-    <t>0.0944,0.0008,0.9390,0.0001</t>
-  </si>
-  <si>
-    <t>0.6251,0.0005,0.5522,0.0000</t>
-  </si>
-  <si>
-    <t>0.7957,0.0002,0.3530,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0005,0.9973,0.0006</t>
-  </si>
-  <si>
-    <t>0.9568,0.0387,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9844,0.0022,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0501,0.5255,0.1356,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.2557,0.0029,0.8016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9773,0.0133,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0204,0.5111,0.6330,0.0000</t>
-  </si>
-  <si>
-    <t>0.0282,0.0875,0.8287,0.0002</t>
-  </si>
-  <si>
-    <t>0.0122,0.8913,0.2011,0.0025</t>
-  </si>
-  <si>
-    <t>0.0806,0.0384,0.8333,0.0004</t>
-  </si>
-  <si>
-    <t>0.8558,0.0001,0.2666,0.0000</t>
-  </si>
-  <si>
-    <t>0.0322,0.0359,0.9120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9984,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0215,0.0001,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.1621,0.2232,0.3958,0.0075</t>
-  </si>
-  <si>
-    <t>0.0021,0.9962,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9965,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.9864,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0099,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.1516,0.0004,0.8974,0.0001</t>
-  </si>
-  <si>
-    <t>0.2119,0.0006,0.8563,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.0006,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0104,0.0014,0.9914,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0018,0.0002,0.0000</t>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9827,0.7885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1841,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0225,0.0103,0.9587,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9871,0.9930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0309,0.9468,0.0091,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0009,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.8489,0.0055,0.1443,0.0001</t>
+  </si>
+  <si>
+    <t>0.0640,0.0026,0.9377,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9812,0.8427,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.6442,0.8706,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0093,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0400,0.0000</t>
+  </si>
+  <si>
+    <t>0.4281,0.0016,0.2612,0.1094</t>
+  </si>
+  <si>
+    <t>0.0041,0.0022,0.0578,0.9861</t>
+  </si>
+  <si>
+    <t>0.1971,0.0031,0.0587,0.6380</t>
+  </si>
+  <si>
+    <t>0.0521,0.0043,0.2770,0.7111</t>
+  </si>
+  <si>
+    <t>0.4750,0.0069,0.2467,0.0844</t>
+  </si>
+  <si>
+    <t>0.0017,0.0047,0.0906,0.9843</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9233,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.3738,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.8540,0.6341,0.0000</t>
+  </si>
+  <si>
+    <t>0.0164,0.2932,0.7299,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9907,0.7342,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9121,0.4325,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0329,0.0024,0.9772,0.0001</t>
+  </si>
+  <si>
+    <t>0.9838,0.0005,0.0084,0.0000</t>
+  </si>
+  <si>
+    <t>0.0425,0.0004,0.9770,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.9940,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.1138,0.8253,0.0304,0.0001</t>
+  </si>
+  <si>
+    <t>0.2637,0.5751,0.0332,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.9849,0.0158,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9974,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.9594,0.0285,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.9160,0.0011,0.0998,0.0001</t>
+  </si>
+  <si>
+    <t>0.8918,0.0008,0.1469,0.0000</t>
+  </si>
+  <si>
+    <t>0.8852,0.0045,0.0884,0.0001</t>
+  </si>
+  <si>
+    <t>0.4873,0.0235,0.4044,0.0002</t>
+  </si>
+  <si>
+    <t>0.0467,0.0141,0.8560,0.0311</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.9800,0.0170,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9968,0.0371,0.0000</t>
+  </si>
+  <si>
+    <t>0.1073,0.8787,0.0037,0.0000</t>
+  </si>
+  <si>
+    <t>0.8914,0.0730,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.9807,0.0141,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9480,0.9463,0.0000</t>
+  </si>
+  <si>
+    <t>0.0538,0.3916,0.2913,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.0013,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.3540,0.0015,0.7441,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0005,0.0105,0.0000</t>
+  </si>
+  <si>
+    <t>0.9362,0.0028,0.0420,0.0001</t>
+  </si>
+  <si>
+    <t>0.9238,0.0002,0.1475,0.0000</t>
+  </si>
+  <si>
+    <t>0.9563,0.0014,0.0345,0.0001</t>
+  </si>
+  <si>
+    <t>0.3826,0.0057,0.2145,0.1823</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0008,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0166,0.9969</t>
+  </si>
+  <si>
+    <t>0.0102,0.0007,0.1774,0.9175</t>
+  </si>
+  <si>
+    <t>0.0000,0.8280,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.1426,0.7845,0.0282,0.0002</t>
+  </si>
+  <si>
+    <t>0.9584,0.0170,0.0095,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0003,0.0090,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.0047,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.7077,0.0542,0.0753,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9908,0.0017,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.8431,0.0128,0.0919,0.0002</t>
+  </si>
+  <si>
+    <t>0.9714,0.0033,0.0126,0.0000</t>
+  </si>
+  <si>
+    <t>0.9846,0.0019,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9819,0.0132,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9763,0.0157,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.6831,0.2083,0.0149,0.0000</t>
+  </si>
+  <si>
+    <t>0.9897,0.0024,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.9925,0.0069,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0023,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0017,0.9989,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1537,0.0004,0.8568,0.0010</t>
-  </si>
-  <si>
-    <t>0.9916,0.0090,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6241,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0047,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.0021,0.9849,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9354,0.9596,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0153,0.9644,0.0153,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0007,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9467,0.0109,0.0191,0.0002</t>
-  </si>
-  <si>
-    <t>0.1147,0.0018,0.9004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.2728,0.9675,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.3021,0.9262,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.1510,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9976,0.1778,0.0000</t>
-  </si>
-  <si>
-    <t>0.1422,0.0014,0.3680,0.2947</t>
-  </si>
-  <si>
-    <t>0.0012,0.0009,0.0149,0.9966</t>
-  </si>
-  <si>
-    <t>0.3760,0.0018,0.0774,0.3376</t>
-  </si>
-  <si>
-    <t>0.0144,0.0041,0.2231,0.9100</t>
-  </si>
-  <si>
-    <t>0.4759,0.0026,0.3167,0.0604</t>
-  </si>
-  <si>
-    <t>0.0021,0.0055,0.0280,0.9925</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.8658,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.5691,0.9466,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.7151,0.9502,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.3335,0.9278,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9527,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.7599,0.6508,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0005,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.3153,0.0012,0.8023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0004,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0141,0.0005,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.9913,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9962,0.0059,0.0000</t>
-  </si>
-  <si>
-    <t>0.0369,0.9570,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.1286,0.8080,0.0253,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9951,0.0071,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9969,0.0036,0.0000</t>
-  </si>
-  <si>
-    <t>0.7908,0.1436,0.0139,0.0001</t>
-  </si>
-  <si>
-    <t>0.6855,0.0068,0.3066,0.0003</t>
-  </si>
-  <si>
-    <t>0.9709,0.0003,0.0336,0.0000</t>
-  </si>
-  <si>
-    <t>0.9293,0.0144,0.0180,0.0001</t>
-  </si>
-  <si>
-    <t>0.2512,0.0977,0.3866,0.0002</t>
-  </si>
-  <si>
-    <t>0.0783,0.0039,0.8729,0.0166</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0148,0.9661,0.0200,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9959,0.1250,0.0000</t>
-  </si>
-  <si>
-    <t>0.2758,0.6886,0.0054,0.0000</t>
-  </si>
-  <si>
-    <t>0.9691,0.0253,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9806,0.0128,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.1733,0.9524,0.0001</t>
-  </si>
-  <si>
-    <t>0.0267,0.5014,0.3654,0.0000</t>
-  </si>
-  <si>
-    <t>0.0124,0.0025,0.9859,0.0000</t>
-  </si>
-  <si>
-    <t>0.7275,0.0019,0.3180,0.0000</t>
-  </si>
-  <si>
-    <t>0.9585,0.0013,0.0302,0.0001</t>
-  </si>
-  <si>
-    <t>0.8230,0.0057,0.1391,0.0001</t>
-  </si>
-  <si>
-    <t>0.9472,0.0003,0.0833,0.0000</t>
-  </si>
-  <si>
-    <t>0.9555,0.0016,0.0308,0.0000</t>
-  </si>
-  <si>
-    <t>0.2527,0.0093,0.2416,0.3203</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0024,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0231,0.9966</t>
-  </si>
-  <si>
-    <t>0.0045,0.0034,0.0899,0.9763</t>
-  </si>
-  <si>
-    <t>0.0002,0.8743,0.9367,0.0000</t>
-  </si>
-  <si>
-    <t>0.9034,0.0432,0.0153,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0033,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9243,0.0003,0.0329,0.0107</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0045,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0006,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.4246,0.0703,0.2484,0.0001</t>
-  </si>
-  <si>
-    <t>0.9929,0.0009,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9923,0.0016,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.5827,0.0290,0.2718,0.0003</t>
-  </si>
-  <si>
-    <t>0.8710,0.0116,0.0695,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0020,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9677,0.0333,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9041,0.0540,0.0104,0.0001</t>
-  </si>
-  <si>
-    <t>0.8493,0.1297,0.0046,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0042,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0036,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0022,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0015,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0004,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0248,0.0008,0.9827,0.0000</t>
-  </si>
-  <si>
-    <t>0.1654,0.0009,0.9172,0.0000</t>
-  </si>
-  <si>
-    <t>0.0155,0.0202,0.9747,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0008,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0307,0.0002,0.9823,0.0001</t>
-  </si>
-  <si>
-    <t>0.0922,0.0036,0.9276,0.0000</t>
-  </si>
-  <si>
-    <t>0.6704,0.0009,0.4889,0.0001</t>
-  </si>
-  <si>
-    <t>0.4312,0.0011,0.7251,0.0000</t>
-  </si>
-  <si>
-    <t>0.8480,0.0041,0.1448,0.0001</t>
-  </si>
-  <si>
-    <t>0.1028,0.0515,0.7459,0.0001</t>
-  </si>
-  <si>
-    <t>0.5316,0.0073,0.4981,0.0001</t>
-  </si>
-  <si>
-    <t>0.9332,0.0026,0.0531,0.0002</t>
-  </si>
-  <si>
-    <t>0.1457,0.0009,0.9124,0.0001</t>
-  </si>
-  <si>
-    <t>0.2822,0.7188,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.2323,0.7712,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9635,0.0417,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9210,0.1100,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9880,0.0217,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8467,0.0019,0.1965,0.0002</t>
-  </si>
-  <si>
-    <t>0.9897,0.0003,0.0063,0.0000</t>
-  </si>
-  <si>
-    <t>0.9750,0.0007,0.0178,0.0000</t>
-  </si>
-  <si>
-    <t>0.9279,0.0004,0.0996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9741,0.0003,0.0319,0.0001</t>
-  </si>
-  <si>
-    <t>0.0245,0.0006,0.9869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0804,0.0378,0.8159,0.0007</t>
-  </si>
-  <si>
-    <t>0.7108,0.0022,0.3131,0.0000</t>
-  </si>
-  <si>
-    <t>0.1486,0.0005,0.9229,0.0000</t>
-  </si>
-  <si>
-    <t>0.1472,0.0137,0.8003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0269,0.0013,0.9851,0.0001</t>
-  </si>
-  <si>
-    <t>0.4574,0.0398,0.3784,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0004,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0133,0.0007,0.9912,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.0062,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.4150,0.0008,0.7245,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0006,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0544,0.0029,0.9477,0.0001</t>
-  </si>
-  <si>
-    <t>0.0537,0.0020,0.9640,0.0000</t>
-  </si>
-  <si>
-    <t>0.9781,0.0003,0.0234,0.0001</t>
-  </si>
-  <si>
-    <t>0.9020,0.0003,0.1643,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0005,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0332,0.0031,0.9718,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0345,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.1732,0.9471,0.0000</t>
-  </si>
-  <si>
-    <t>0.2174,0.0157,0.7137,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.0002,0.9930,0.0001</t>
-  </si>
-  <si>
-    <t>0.0432,0.0001,0.9673,0.0001</t>
-  </si>
-  <si>
-    <t>0.8515,0.0009,0.2040,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0009,0.9876,0.0027</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8265,0.0012,0.0596,0.0307</t>
-  </si>
-  <si>
-    <t>0.1700,0.0008,0.7503,0.0295</t>
-  </si>
-  <si>
-    <t>0.0201,0.0005,0.1674,0.8362</t>
-  </si>
-  <si>
-    <t>0.0096,0.0006,0.0210,0.9844</t>
-  </si>
-  <si>
-    <t>0.9821,0.0008,0.0101,0.0004</t>
+    <t>0.0092,0.0024,0.9916,0.0001</t>
+  </si>
+  <si>
+    <t>0.1176,0.0017,0.9249,0.0000</t>
+  </si>
+  <si>
+    <t>0.0150,0.0002,0.9922,0.0000</t>
+  </si>
+  <si>
+    <t>0.0221,0.0055,0.9787,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.0003,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0004,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.5396,0.0021,0.5620,0.0000</t>
+  </si>
+  <si>
+    <t>0.1455,0.0014,0.9149,0.0001</t>
+  </si>
+  <si>
+    <t>0.6157,0.0063,0.3738,0.0000</t>
+  </si>
+  <si>
+    <t>0.4105,0.0075,0.6080,0.0000</t>
+  </si>
+  <si>
+    <t>0.2686,0.0099,0.7071,0.0001</t>
+  </si>
+  <si>
+    <t>0.8942,0.0017,0.1194,0.0000</t>
+  </si>
+  <si>
+    <t>0.5906,0.0032,0.4768,0.0002</t>
+  </si>
+  <si>
+    <t>0.4476,0.0012,0.6886,0.0001</t>
+  </si>
+  <si>
+    <t>0.3393,0.6252,0.0081,0.0000</t>
+  </si>
+  <si>
+    <t>0.1732,0.8435,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.6027,0.3683,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0155,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9721,0.0381,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7843,0.0080,0.1586,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0002,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.9593,0.0006,0.0410,0.0001</t>
+  </si>
+  <si>
+    <t>0.9316,0.0007,0.0849,0.0000</t>
+  </si>
+  <si>
+    <t>0.9567,0.0004,0.0614,0.0000</t>
+  </si>
+  <si>
+    <t>0.0174,0.0005,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.1558,0.0118,0.8004,0.0001</t>
+  </si>
+  <si>
+    <t>0.7177,0.0051,0.2306,0.0000</t>
+  </si>
+  <si>
+    <t>0.1328,0.0013,0.9042,0.0001</t>
+  </si>
+  <si>
+    <t>0.0476,0.0070,0.9382,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0172,0.0015,0.9914,0.0001</t>
+  </si>
+  <si>
+    <t>0.4114,0.0230,0.5292,0.0001</t>
+  </si>
+  <si>
+    <t>0.9914,0.0003,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.7654,0.0005,0.3676,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0078,0.9850,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.4300,0.0028,0.6498,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0134,0.0043,0.9824,0.0000</t>
+  </si>
+  <si>
+    <t>0.0194,0.0006,0.9876,0.0000</t>
+  </si>
+  <si>
+    <t>0.9827,0.0003,0.0158,0.0001</t>
+  </si>
+  <si>
+    <t>0.9206,0.0007,0.0891,0.0000</t>
+  </si>
+  <si>
+    <t>0.9604,0.0008,0.0362,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2622,0.0100,0.7133,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0043,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.3693,0.8320,0.0001</t>
+  </si>
+  <si>
+    <t>0.3973,0.0075,0.6164,0.0002</t>
+  </si>
+  <si>
+    <t>0.0125,0.0003,0.9900,0.0001</t>
+  </si>
+  <si>
+    <t>0.5935,0.0001,0.5990,0.0001</t>
+  </si>
+  <si>
+    <t>0.7320,0.0004,0.4215,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0005,0.9910,0.0007</t>
+  </si>
+  <si>
+    <t>0.9940,0.0003,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9269,0.0015,0.0237,0.0128</t>
+  </si>
+  <si>
+    <t>0.3112,0.0012,0.6053,0.0272</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.0785,0.9850</t>
+  </si>
+  <si>
+    <t>0.2244,0.0004,0.0335,0.6453</t>
+  </si>
+  <si>
+    <t>0.9739,0.0006,0.0185,0.0007</t>
   </si>
 </sst>
 </file>
@@ -1821,7 +1830,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1835,7 +1844,7 @@
         <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1849,7 +1858,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1860,10 +1869,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1877,7 +1886,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1891,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1905,7 +1914,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1919,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1947,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1961,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1975,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1989,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2003,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2017,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2031,7 +2040,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2045,7 +2054,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2059,7 +2068,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2073,7 +2082,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2084,10 +2093,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2101,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2115,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2129,7 +2138,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2143,7 +2152,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2157,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2171,7 +2180,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2182,10 +2191,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2199,7 +2208,7 @@
         <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2213,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2227,7 +2236,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2241,7 +2250,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2255,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2269,7 +2278,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2283,7 +2292,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2297,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2311,7 +2320,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2322,10 +2331,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2339,7 +2348,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2353,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2367,7 +2376,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2378,10 +2387,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2395,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2409,7 +2418,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2423,7 +2432,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2434,10 +2443,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2451,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2465,7 +2474,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2479,7 +2488,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2493,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2507,7 +2516,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2521,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2535,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2549,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2563,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2577,7 +2586,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2591,7 +2600,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2605,7 +2614,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2619,7 +2628,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2633,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2647,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2661,7 +2670,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2675,7 +2684,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2689,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2703,7 +2712,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2717,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2731,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2745,7 +2754,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2759,7 +2768,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2773,7 +2782,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2787,7 +2796,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2801,7 +2810,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2812,10 +2821,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2826,10 +2835,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2843,7 +2852,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2857,7 +2866,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2868,10 +2877,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2885,7 +2894,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2896,10 +2905,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2913,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2924,10 +2933,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2941,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2955,7 +2964,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2966,10 +2975,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2983,7 +2992,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2997,7 +3006,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3011,7 +3020,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3022,10 +3031,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3039,7 +3048,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3053,7 +3062,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3067,7 +3076,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3081,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3095,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3123,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3137,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3151,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3165,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3179,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3193,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3207,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3221,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3235,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3249,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3263,7 +3272,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3277,7 +3286,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3291,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3305,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3319,7 +3328,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3333,7 +3342,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3347,7 +3356,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3361,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3375,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3389,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3403,7 +3412,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3417,7 +3426,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3431,7 +3440,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3445,7 +3454,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3456,10 +3465,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3473,7 +3482,7 @@
         <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3487,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3501,7 +3510,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3515,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3529,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3543,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3557,7 +3566,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3571,7 +3580,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3585,7 +3594,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3599,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3613,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3627,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3641,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3655,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3669,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3683,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3694,10 +3703,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3708,10 +3717,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D137" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3725,7 +3734,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3736,10 +3745,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3753,7 +3762,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3767,7 +3776,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3781,7 +3790,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3795,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3806,10 +3815,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3823,7 +3832,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3837,7 +3846,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3851,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3865,7 +3874,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3879,7 +3888,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3890,10 +3899,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3907,7 +3916,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3921,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3935,7 +3944,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3949,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3963,7 +3972,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3977,7 +3986,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3991,7 +4000,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4005,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4019,7 +4028,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4033,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4047,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4061,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4075,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4089,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4103,7 +4112,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4117,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4131,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>400</v>
+        <v>318</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4145,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4159,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4173,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4187,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4201,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>269</v>
+        <v>404</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4215,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4229,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4243,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4257,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4271,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4285,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4299,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4313,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4327,7 +4336,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4341,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4355,7 +4364,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4369,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4383,7 +4392,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4397,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4411,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4425,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4439,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4450,10 +4459,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4464,10 +4473,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4478,10 +4487,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4492,10 +4501,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4509,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4523,7 +4532,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4537,7 +4546,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4551,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4565,7 +4574,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4579,7 +4588,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4593,7 +4602,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4607,7 +4616,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4621,7 +4630,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4635,7 +4644,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4649,7 +4658,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4663,7 +4672,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4677,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4691,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4705,7 +4714,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4719,7 +4728,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4733,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D210" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4747,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4761,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4775,7 +4784,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4789,7 +4798,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4803,7 +4812,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4817,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4831,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>442</v>
+        <v>272</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4845,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4859,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4873,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4887,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4898,10 +4907,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4915,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4926,10 +4935,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4943,7 +4952,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4957,7 +4966,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4971,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4985,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4999,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5013,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5027,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5041,7 +5050,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5055,7 +5064,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5069,7 +5078,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5083,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5097,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>458</v>
+        <v>272</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5111,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5125,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>459</v>
+        <v>375</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5139,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5153,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>347</v>
+        <v>462</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5167,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5181,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5195,7 +5204,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5209,7 +5218,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5223,7 +5232,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5237,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5251,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5262,10 +5271,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5279,7 +5288,7 @@
         <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5293,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5307,7 +5316,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5321,7 +5330,7 @@
         <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5335,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D253" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5349,7 +5358,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5363,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5377,7 +5386,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
